--- a/DataPreparation/BloodMarkers/JH_Serum_Zentrallabor_2022-08-19.xlsx
+++ b/DataPreparation/BloodMarkers/JH_Serum_Zentrallabor_2022-08-19.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Q:\IPE-A-Epidemiologie\Virginie_Stanislas\Projects\2206_JoghurtStudy\Analysis\DataPreparation\BloodMarkers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Q:\IPE-P-Joghurtstudie\Joghurt und Haferflocken\Analysis\Public_repository\GitHub_repository\IPE_yogurt_rolledOat_microbiome\DataPreparation\BloodMarkers\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -2690,9 +2690,6 @@
     <t>JH-021-1</t>
   </si>
   <si>
-    <t>KT</t>
-  </si>
-  <si>
     <t>JH-021-3</t>
   </si>
   <si>
@@ -2822,9 +2819,6 @@
     <t>JH-033-1</t>
   </si>
   <si>
-    <t>KM</t>
-  </si>
-  <si>
     <t>JH-033-3</t>
   </si>
   <si>
@@ -4938,6 +4932,12 @@
   </si>
   <si>
     <t>126b</t>
+  </si>
+  <si>
+    <t>xxx</t>
+  </si>
+  <si>
+    <t>zzz</t>
   </si>
 </sst>
 </file>
@@ -5908,10 +5908,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>3</v>
@@ -5929,20 +5929,20 @@
         <v>7</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="M1" s="5"/>
       <c r="N1" s="5" t="s">
+        <v>1617</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>1618</v>
+      </c>
+      <c r="P1" s="5" t="s">
         <v>1619</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>1620</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>1621</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -5959,7 +5959,7 @@
         <v>140</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>10</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="K2" s="2"/>
       <c r="P2" s="7" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -6343,7 +6343,7 @@
         <v>64</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="L13" s="15" t="s">
         <v>756</v>
@@ -6757,7 +6757,7 @@
         <v>106</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="L25" s="15" t="s">
         <v>83</v>
@@ -7138,7 +7138,7 @@
         <v>29</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="L36" s="15" t="s">
         <v>151</v>
@@ -7515,7 +7515,7 @@
         <v>145</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="L47" s="15" t="s">
         <v>40</v>
@@ -7892,7 +7892,7 @@
         <v>55</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="L58" s="15" t="s">
         <v>302</v>
@@ -8269,7 +8269,7 @@
         <v>241</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="L69" s="15" t="s">
         <v>67</v>
@@ -8756,7 +8756,7 @@
         <v>82</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
@@ -8773,13 +8773,13 @@
         <v>20220812</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>888</v>
+        <v>1636</v>
       </c>
       <c r="F85" s="15" t="s">
         <v>13</v>
@@ -8797,7 +8797,7 @@
         <v>68</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="L85" s="15" t="s">
         <v>93</v>
@@ -8826,7 +8826,7 @@
         <v>83</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>13</v>
@@ -8859,7 +8859,7 @@
         <v>84</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F87" s="6" t="s">
         <v>13</v>
@@ -8892,7 +8892,7 @@
         <v>85</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>13</v>
@@ -8925,7 +8925,7 @@
         <v>86</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>13</v>
@@ -8958,7 +8958,7 @@
         <v>87</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>13</v>
@@ -8991,7 +8991,7 @@
         <v>88</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>13</v>
@@ -9024,7 +9024,7 @@
         <v>89</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>13</v>
@@ -9057,7 +9057,7 @@
         <v>90</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F93" s="6" t="s">
         <v>13</v>
@@ -9090,7 +9090,7 @@
         <v>91</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>13</v>
@@ -9123,7 +9123,7 @@
         <v>92</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F95" s="6" t="s">
         <v>13</v>
@@ -9156,7 +9156,7 @@
         <v>93</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>13</v>
@@ -9189,7 +9189,7 @@
         <v>94</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>13</v>
@@ -9222,7 +9222,7 @@
         <v>95</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>13</v>
@@ -9255,7 +9255,7 @@
         <v>96</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>13</v>
@@ -9288,7 +9288,7 @@
         <v>97</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>13</v>
@@ -9325,7 +9325,7 @@
         <v>98</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F101" s="15" t="s">
         <v>13</v>
@@ -9343,7 +9343,7 @@
         <v>19</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="L101" s="15" t="s">
         <v>137</v>
@@ -9372,7 +9372,7 @@
         <v>99</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>13</v>
@@ -9405,7 +9405,7 @@
         <v>100</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F103" s="6" t="s">
         <v>13</v>
@@ -9438,7 +9438,7 @@
         <v>101</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>13</v>
@@ -9471,7 +9471,7 @@
         <v>102</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F105" s="6" t="s">
         <v>13</v>
@@ -9504,7 +9504,7 @@
         <v>103</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>13</v>
@@ -9537,7 +9537,7 @@
         <v>104</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>13</v>
@@ -9570,7 +9570,7 @@
         <v>105</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>13</v>
@@ -9603,7 +9603,7 @@
         <v>106</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F109" s="6" t="s">
         <v>13</v>
@@ -9636,7 +9636,7 @@
         <v>107</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>13</v>
@@ -9669,7 +9669,7 @@
         <v>108</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F111" s="6" t="s">
         <v>13</v>
@@ -9702,7 +9702,7 @@
         <v>109</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F112" s="15" t="s">
         <v>13</v>
@@ -9720,7 +9720,7 @@
         <v>68</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="L112" s="15" t="s">
         <v>504</v>
@@ -9749,7 +9749,7 @@
         <v>110</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F113" s="6" t="s">
         <v>13</v>
@@ -9782,7 +9782,7 @@
         <v>111</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>13</v>
@@ -9815,7 +9815,7 @@
         <v>112</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>13</v>
@@ -9848,7 +9848,7 @@
         <v>113</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>13</v>
@@ -9881,7 +9881,7 @@
         <v>114</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>13</v>
@@ -9914,7 +9914,7 @@
         <v>115</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>13</v>
@@ -9947,7 +9947,7 @@
         <v>116</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>13</v>
@@ -9980,7 +9980,7 @@
         <v>117</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>13</v>
@@ -10013,7 +10013,7 @@
         <v>118</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F121" s="6" t="s">
         <v>13</v>
@@ -10046,7 +10046,7 @@
         <v>119</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>13</v>
@@ -10079,7 +10079,7 @@
         <v>120</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>13</v>
@@ -10112,7 +10112,7 @@
         <v>121</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>13</v>
@@ -10145,7 +10145,7 @@
         <v>122</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F125" s="6" t="s">
         <v>13</v>
@@ -10178,7 +10178,7 @@
         <v>123</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>13</v>
@@ -10211,7 +10211,7 @@
         <v>124</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F127" s="6" t="s">
         <v>13</v>
@@ -10244,7 +10244,7 @@
         <v>125</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>13</v>
@@ -10273,7 +10273,7 @@
         <v>126</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="F129" s="6"/>
       <c r="G129" s="6"/>
@@ -10290,13 +10290,13 @@
         <v>20220812</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="D130" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E130" s="4" t="s">
         <v>1637</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>932</v>
       </c>
       <c r="F130" s="15" t="s">
         <v>13</v>
@@ -10314,7 +10314,7 @@
         <v>68</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="L130" s="15" t="s">
         <v>776</v>
@@ -10343,7 +10343,7 @@
         <v>127</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="F131" s="6" t="s">
         <v>13</v>
@@ -10376,7 +10376,7 @@
         <v>128</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>13</v>
@@ -10409,7 +10409,7 @@
         <v>129</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="F133" s="6" t="s">
         <v>13</v>
@@ -10442,7 +10442,7 @@
         <v>130</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>13</v>
@@ -10475,7 +10475,7 @@
         <v>131</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="F135" s="6" t="s">
         <v>13</v>
@@ -10508,7 +10508,7 @@
         <v>132</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>13</v>
@@ -10541,7 +10541,7 @@
         <v>133</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="F137" s="6" t="s">
         <v>13</v>
@@ -10574,7 +10574,7 @@
         <v>134</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>13</v>
@@ -10607,7 +10607,7 @@
         <v>135</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="F139" s="15" t="s">
         <v>13</v>
@@ -10625,7 +10625,7 @@
         <v>29</v>
       </c>
       <c r="K139" s="4" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="L139" s="15" t="s">
         <v>339</v>
@@ -10654,7 +10654,7 @@
         <v>136</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>13</v>
@@ -10687,7 +10687,7 @@
         <v>137</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="F141" s="6" t="s">
         <v>13</v>
@@ -10720,7 +10720,7 @@
         <v>138</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>13</v>
@@ -10753,7 +10753,7 @@
         <v>139</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="F143" s="6" t="s">
         <v>13</v>
@@ -10786,7 +10786,7 @@
         <v>141</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>13</v>
@@ -10819,7 +10819,7 @@
         <v>142</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>13</v>
@@ -10852,7 +10852,7 @@
         <v>143</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>13</v>
@@ -10885,7 +10885,7 @@
         <v>144</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="F147" s="6" t="s">
         <v>13</v>
@@ -10918,7 +10918,7 @@
         <v>145</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>13</v>
@@ -10951,7 +10951,7 @@
         <v>146</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="F149" s="6" t="s">
         <v>13</v>
@@ -10984,7 +10984,7 @@
         <v>147</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>13</v>
@@ -11017,7 +11017,7 @@
         <v>148</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="F151" s="6" t="s">
         <v>13</v>
@@ -11054,7 +11054,7 @@
         <v>149</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="F152" s="15" t="s">
         <v>13</v>
@@ -11072,7 +11072,7 @@
         <v>72</v>
       </c>
       <c r="K152" s="4" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="L152" s="15" t="s">
         <v>133</v>
@@ -11101,7 +11101,7 @@
         <v>150</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="F153" s="6" t="s">
         <v>13</v>
@@ -11134,7 +11134,7 @@
         <v>151</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>13</v>
@@ -11167,7 +11167,7 @@
         <v>152</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="F155" s="6" t="s">
         <v>13</v>
@@ -11200,7 +11200,7 @@
         <v>153</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>13</v>
@@ -11233,7 +11233,7 @@
         <v>154</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="F157" s="6" t="s">
         <v>13</v>
@@ -11266,7 +11266,7 @@
         <v>155</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>13</v>
@@ -11299,7 +11299,7 @@
         <v>156</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="F159" s="6" t="s">
         <v>13</v>
@@ -11332,7 +11332,7 @@
         <v>157</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>13</v>
@@ -11365,7 +11365,7 @@
         <v>158</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F161" s="6" t="s">
         <v>13</v>
@@ -11402,7 +11402,7 @@
         <v>159</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="F162" s="15" t="s">
         <v>13</v>
@@ -11420,7 +11420,7 @@
         <v>110</v>
       </c>
       <c r="K162" s="4" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="L162" s="15" t="s">
         <v>222</v>
@@ -11449,7 +11449,7 @@
         <v>160</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="F163" s="6" t="s">
         <v>13</v>
@@ -11482,7 +11482,7 @@
         <v>161</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>13</v>
@@ -11515,7 +11515,7 @@
         <v>162</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="F165" s="6" t="s">
         <v>13</v>
@@ -11548,7 +11548,7 @@
         <v>163</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>13</v>
@@ -11581,7 +11581,7 @@
         <v>164</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="F167" s="6" t="s">
         <v>13</v>
@@ -11614,7 +11614,7 @@
         <v>165</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>13</v>
@@ -11647,7 +11647,7 @@
         <v>166</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="F169" s="6" t="s">
         <v>13</v>
@@ -11680,7 +11680,7 @@
         <v>167</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>13</v>
@@ -11713,7 +11713,7 @@
         <v>168</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="F171" s="6" t="s">
         <v>13</v>
@@ -11746,7 +11746,7 @@
         <v>169</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>13</v>
@@ -11779,7 +11779,7 @@
         <v>170</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="F173" s="6" t="s">
         <v>13</v>
@@ -11812,7 +11812,7 @@
         <v>171</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>13</v>
@@ -11849,7 +11849,7 @@
         <v>172</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="F175" s="15" t="s">
         <v>13</v>
@@ -11867,7 +11867,7 @@
         <v>55</v>
       </c>
       <c r="K175" s="4" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="L175" s="15" t="s">
         <v>120</v>
@@ -11896,7 +11896,7 @@
         <v>173</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>13</v>
@@ -11915,7 +11915,7 @@
       </c>
       <c r="K176" s="2"/>
       <c r="P176" s="7" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="177" spans="1:16" x14ac:dyDescent="0.25">
@@ -11932,7 +11932,7 @@
         <v>174</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="F177" s="6" t="s">
         <v>13</v>
@@ -11965,7 +11965,7 @@
         <v>175</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>13</v>
@@ -11998,7 +11998,7 @@
         <v>176</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="F179" s="6" t="s">
         <v>13</v>
@@ -12031,7 +12031,7 @@
         <v>177</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>13</v>
@@ -12050,7 +12050,7 @@
       </c>
       <c r="K180" s="2"/>
       <c r="P180" s="7" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="181" spans="1:16" x14ac:dyDescent="0.25">
@@ -12067,7 +12067,7 @@
         <v>178</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="F181" s="6" t="s">
         <v>13</v>
@@ -12100,7 +12100,7 @@
         <v>179</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>13</v>
@@ -12133,7 +12133,7 @@
         <v>180</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="F183" s="6" t="s">
         <v>13</v>
@@ -12166,7 +12166,7 @@
         <v>181</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>13</v>
@@ -12199,7 +12199,7 @@
         <v>182</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="F185" s="6" t="s">
         <v>13</v>
@@ -12232,7 +12232,7 @@
         <v>183</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>13</v>
@@ -12265,7 +12265,7 @@
         <v>184</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="F187" s="6" t="s">
         <v>13</v>
@@ -12298,7 +12298,7 @@
         <v>185</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="F188" s="15" t="s">
         <v>13</v>
@@ -12316,7 +12316,7 @@
         <v>94</v>
       </c>
       <c r="K188" s="4" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="L188" s="15" t="s">
         <v>151</v>
@@ -12345,7 +12345,7 @@
         <v>186</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="F189" s="6" t="s">
         <v>13</v>
@@ -12378,7 +12378,7 @@
         <v>187</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>13</v>
@@ -12411,7 +12411,7 @@
         <v>188</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="F191" s="6" t="s">
         <v>13</v>
@@ -12444,7 +12444,7 @@
         <v>189</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>13</v>
@@ -12477,7 +12477,7 @@
         <v>190</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="F193" s="6" t="s">
         <v>13</v>
@@ -12510,7 +12510,7 @@
         <v>191</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>13</v>
@@ -12543,7 +12543,7 @@
         <v>192</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="F195" s="6" t="s">
         <v>13</v>
@@ -12576,7 +12576,7 @@
         <v>193</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>13</v>
@@ -12609,7 +12609,7 @@
         <v>194</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="F197" s="6" t="s">
         <v>13</v>
@@ -12642,7 +12642,7 @@
         <v>195</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>13</v>
@@ -12675,7 +12675,7 @@
         <v>196</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="F199" s="6" t="s">
         <v>13</v>
@@ -12708,7 +12708,7 @@
         <v>197</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>13</v>
@@ -12741,7 +12741,7 @@
         <v>198</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="F201" s="6" t="s">
         <v>13</v>
@@ -12774,7 +12774,7 @@
         <v>199</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>13</v>
@@ -12807,7 +12807,7 @@
         <v>200</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="F203" s="6" t="s">
         <v>13</v>
@@ -12840,7 +12840,7 @@
         <v>201</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>13</v>
@@ -12873,7 +12873,7 @@
         <v>202</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="F205" s="15" t="s">
         <v>13</v>
@@ -12891,7 +12891,7 @@
         <v>24</v>
       </c>
       <c r="K205" s="4" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="L205" s="15" t="s">
         <v>457</v>
@@ -12920,7 +12920,7 @@
         <v>203</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>13</v>
@@ -12953,7 +12953,7 @@
         <v>204</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="F207" s="6" t="s">
         <v>13</v>
@@ -12986,7 +12986,7 @@
         <v>205</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="F208" s="6" t="s">
         <v>13</v>
@@ -13019,7 +13019,7 @@
         <v>206</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="F209" s="6" t="s">
         <v>13</v>
@@ -13052,7 +13052,7 @@
         <v>207</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="F210" s="6" t="s">
         <v>13</v>
@@ -13085,7 +13085,7 @@
         <v>208</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="F211" s="6" t="s">
         <v>13</v>
@@ -13118,7 +13118,7 @@
         <v>209</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="F212" s="6" t="s">
         <v>13</v>
@@ -13151,7 +13151,7 @@
         <v>210</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="F213" s="6" t="s">
         <v>13</v>
@@ -13184,7 +13184,7 @@
         <v>211</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="F214" s="15" t="s">
         <v>13</v>
@@ -13202,7 +13202,7 @@
         <v>72</v>
       </c>
       <c r="K214" s="4" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="L214" s="15" t="s">
         <v>430</v>
@@ -13231,7 +13231,7 @@
         <v>212</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="F215" s="6" t="s">
         <v>13</v>
@@ -13269,7 +13269,7 @@
         <v>213</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="F216" s="6" t="s">
         <v>13</v>
@@ -13302,7 +13302,7 @@
         <v>214</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="F217" s="6" t="s">
         <v>13</v>
@@ -13335,7 +13335,7 @@
         <v>215</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>13</v>
@@ -13368,7 +13368,7 @@
         <v>216</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="F219" s="6" t="s">
         <v>13</v>
@@ -13401,7 +13401,7 @@
         <v>217</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="F220" s="6" t="s">
         <v>13</v>
@@ -13434,7 +13434,7 @@
         <v>218</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="F221" s="6" t="s">
         <v>13</v>
@@ -13467,7 +13467,7 @@
         <v>219</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="F222" s="6" t="s">
         <v>13</v>
@@ -13500,7 +13500,7 @@
         <v>220</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="F223" s="6" t="s">
         <v>13</v>
@@ -13533,7 +13533,7 @@
         <v>221</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="F224" s="6" t="s">
         <v>13</v>
@@ -13566,7 +13566,7 @@
         <v>222</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="F225" s="6" t="s">
         <v>13</v>
@@ -13599,7 +13599,7 @@
         <v>223</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="F226" s="6" t="s">
         <v>13</v>
@@ -13632,7 +13632,7 @@
         <v>224</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="F227" s="6" t="s">
         <v>13</v>
@@ -13665,7 +13665,7 @@
         <v>225</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="F228" s="6" t="s">
         <v>13</v>
@@ -13698,7 +13698,7 @@
         <v>226</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="F229" s="6" t="s">
         <v>13</v>
@@ -13731,7 +13731,7 @@
         <v>227</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="F230" s="6" t="s">
         <v>13</v>
@@ -13764,7 +13764,7 @@
         <v>228</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="F231" s="15" t="s">
         <v>13</v>
@@ -13782,7 +13782,7 @@
         <v>72</v>
       </c>
       <c r="K231" s="4" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="L231" s="15" t="s">
         <v>415</v>
@@ -13811,7 +13811,7 @@
         <v>229</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="F232" s="6" t="s">
         <v>13</v>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="K232" s="2"/>
       <c r="P232" s="7" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.25">
@@ -13847,7 +13847,7 @@
         <v>230</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="F233" s="6" t="s">
         <v>13</v>
@@ -13880,7 +13880,7 @@
         <v>231</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="F234" s="6" t="s">
         <v>13</v>
@@ -13913,7 +13913,7 @@
         <v>232</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="F235" s="6" t="s">
         <v>13</v>
@@ -13946,7 +13946,7 @@
         <v>233</v>
       </c>
       <c r="E236" s="4" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="F236" s="15" t="s">
         <v>13</v>
@@ -13964,7 +13964,7 @@
         <v>55</v>
       </c>
       <c r="K236" s="4" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="L236" s="15" t="s">
         <v>795</v>
@@ -13993,7 +13993,7 @@
         <v>234</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="F237" s="6" t="s">
         <v>13</v>
@@ -14026,7 +14026,7 @@
         <v>235</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="F238" s="6" t="s">
         <v>13</v>
@@ -14059,7 +14059,7 @@
         <v>236</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="F239" s="6" t="s">
         <v>13</v>
@@ -14092,7 +14092,7 @@
         <v>237</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="F240" s="6" t="s">
         <v>13</v>
@@ -14125,7 +14125,7 @@
         <v>238</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="F241" s="6" t="s">
         <v>13</v>
@@ -14158,7 +14158,7 @@
         <v>239</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="F242" s="6" t="s">
         <v>13</v>
@@ -14191,7 +14191,7 @@
         <v>240</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="F243" s="6" t="s">
         <v>13</v>
@@ -14224,7 +14224,7 @@
         <v>241</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="F244" s="6" t="s">
         <v>13</v>
@@ -14257,7 +14257,7 @@
         <v>242</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="F245" s="6" t="s">
         <v>13</v>
@@ -14290,7 +14290,7 @@
         <v>243</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="F246" s="6" t="s">
         <v>13</v>
@@ -14323,7 +14323,7 @@
         <v>244</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="F247" s="6" t="s">
         <v>13</v>
@@ -14356,7 +14356,7 @@
         <v>245</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="F248" s="6" t="s">
         <v>13</v>
@@ -14389,7 +14389,7 @@
         <v>246</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="F249" s="6" t="s">
         <v>13</v>
@@ -14422,7 +14422,7 @@
         <v>247</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="F250" s="6" t="s">
         <v>13</v>
@@ -14455,7 +14455,7 @@
         <v>248</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="F251" s="6" t="s">
         <v>13</v>
@@ -14488,7 +14488,7 @@
         <v>249</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="F252" s="6" t="s">
         <v>13</v>
@@ -14521,7 +14521,7 @@
         <v>250</v>
       </c>
       <c r="E253" s="4" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="F253" s="15" t="s">
         <v>13</v>
@@ -14539,7 +14539,7 @@
         <v>19</v>
       </c>
       <c r="K253" s="4" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="L253" s="15" t="s">
         <v>151</v>
@@ -14568,7 +14568,7 @@
         <v>251</v>
       </c>
       <c r="E254" s="9" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F254" s="6" t="s">
         <v>13</v>
@@ -14606,7 +14606,7 @@
         <v>252</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="F255" s="6" t="s">
         <v>13</v>
@@ -14639,7 +14639,7 @@
         <v>253</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F256" s="6" t="s">
         <v>13</v>
@@ -14672,7 +14672,7 @@
         <v>254</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="F257" s="6" t="s">
         <v>13</v>
@@ -14705,7 +14705,7 @@
         <v>255</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="F258" s="6" t="s">
         <v>13</v>
@@ -14738,7 +14738,7 @@
         <v>256</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="F259" s="6" t="s">
         <v>13</v>
@@ -14771,7 +14771,7 @@
         <v>257</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="F260" s="6" t="s">
         <v>13</v>
@@ -14804,7 +14804,7 @@
         <v>258</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F261" s="6" t="s">
         <v>13</v>
@@ -14837,7 +14837,7 @@
         <v>259</v>
       </c>
       <c r="E262" s="4" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F262" s="15" t="s">
         <v>13</v>
@@ -14855,7 +14855,7 @@
         <v>673</v>
       </c>
       <c r="K262" s="4" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="L262" s="15" t="s">
         <v>171</v>
@@ -14884,7 +14884,7 @@
         <v>260</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="F263" s="6" t="s">
         <v>13</v>
@@ -14917,7 +14917,7 @@
         <v>261</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="F264" s="6" t="s">
         <v>13</v>
@@ -14950,7 +14950,7 @@
         <v>262</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="F265" s="6" t="s">
         <v>13</v>
@@ -14983,7 +14983,7 @@
         <v>263</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="F266" s="6" t="s">
         <v>13</v>
@@ -15016,7 +15016,7 @@
         <v>264</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="F267" s="6" t="s">
         <v>13</v>
@@ -15049,7 +15049,7 @@
         <v>265</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="F268" s="6" t="s">
         <v>13</v>
@@ -15082,7 +15082,7 @@
         <v>266</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="F269" s="6" t="s">
         <v>13</v>
@@ -15115,7 +15115,7 @@
         <v>267</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="F270" s="6" t="s">
         <v>13</v>
@@ -15148,7 +15148,7 @@
         <v>268</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="F271" s="6" t="s">
         <v>13</v>
@@ -15181,7 +15181,7 @@
         <v>269</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F272" s="6" t="s">
         <v>13</v>
@@ -15214,7 +15214,7 @@
         <v>270</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="F273" s="6" t="s">
         <v>13</v>
@@ -15247,7 +15247,7 @@
         <v>271</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="F274" s="6" t="s">
         <v>13</v>
@@ -15280,7 +15280,7 @@
         <v>272</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="F275" s="6" t="s">
         <v>13</v>
@@ -15313,7 +15313,7 @@
         <v>273</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="F276" s="6" t="s">
         <v>13</v>
@@ -15346,7 +15346,7 @@
         <v>274</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F277" s="6" t="s">
         <v>13</v>
@@ -15379,7 +15379,7 @@
         <v>275</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="F278" s="6" t="s">
         <v>13</v>
@@ -15412,7 +15412,7 @@
         <v>276</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="F279" s="6" t="s">
         <v>13</v>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="K279" s="2"/>
       <c r="P279" s="16" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="280" spans="1:16" x14ac:dyDescent="0.25">
@@ -15448,7 +15448,7 @@
         <v>277</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="F280" s="6" t="s">
         <v>13</v>
@@ -15481,7 +15481,7 @@
         <v>278</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="F281" s="6" t="s">
         <v>13</v>
@@ -15514,7 +15514,7 @@
         <v>279</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="F282" s="6" t="s">
         <v>13</v>
@@ -15551,7 +15551,7 @@
         <v>280</v>
       </c>
       <c r="E283" s="4" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="F283" s="15" t="s">
         <v>13</v>
@@ -15569,7 +15569,7 @@
         <v>55</v>
       </c>
       <c r="K283" s="4" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="L283" s="15" t="s">
         <v>120</v>
@@ -15598,7 +15598,7 @@
         <v>281</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="F284" s="6" t="s">
         <v>13</v>
@@ -15631,7 +15631,7 @@
         <v>282</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="F285" s="6" t="s">
         <v>13</v>
@@ -15664,7 +15664,7 @@
         <v>283</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="F286" s="6" t="s">
         <v>13</v>
@@ -15697,7 +15697,7 @@
         <v>284</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="F287" s="6" t="s">
         <v>13</v>
@@ -15730,7 +15730,7 @@
         <v>285</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="F288" s="6" t="s">
         <v>13</v>
@@ -15763,7 +15763,7 @@
         <v>286</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="F289" s="6" t="s">
         <v>13</v>
@@ -15796,7 +15796,7 @@
         <v>287</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="F290" s="6" t="s">
         <v>13</v>
@@ -15829,7 +15829,7 @@
         <v>288</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="F291" s="6" t="s">
         <v>13</v>
@@ -15862,7 +15862,7 @@
         <v>289</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="F292" s="6" t="s">
         <v>13</v>
@@ -15895,7 +15895,7 @@
         <v>290</v>
       </c>
       <c r="E293" s="4" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="F293" s="15" t="s">
         <v>13</v>
@@ -15913,7 +15913,7 @@
         <v>110</v>
       </c>
       <c r="K293" s="4" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="L293" s="15" t="s">
         <v>267</v>
@@ -15942,7 +15942,7 @@
         <v>291</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="F294" s="6" t="s">
         <v>13</v>
@@ -15975,7 +15975,7 @@
         <v>292</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="F295" s="6" t="s">
         <v>13</v>
@@ -16008,7 +16008,7 @@
         <v>293</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="F296" s="6" t="s">
         <v>13</v>
@@ -16041,7 +16041,7 @@
         <v>294</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="F297" s="6" t="s">
         <v>13</v>
@@ -16074,7 +16074,7 @@
         <v>295</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="F298" s="6" t="s">
         <v>13</v>
@@ -16107,7 +16107,7 @@
         <v>296</v>
       </c>
       <c r="E299" s="9" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="F299" s="6" t="s">
         <v>13</v>
@@ -16132,19 +16132,19 @@
     </row>
     <row r="300" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B300" s="13">
         <v>20220826</v>
       </c>
       <c r="C300" s="15" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D300" s="3">
         <v>297</v>
       </c>
       <c r="E300" s="4" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="F300" s="15"/>
       <c r="G300" s="15" t="s">
@@ -16160,7 +16160,7 @@
         <v>68</v>
       </c>
       <c r="K300" s="4" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="L300" s="15" t="s">
         <v>86</v>
@@ -16177,19 +16177,19 @@
     </row>
     <row r="301" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A301" s="10" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="B301" s="13">
         <v>20220826</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="D301" s="1">
         <v>298</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="F301" s="6"/>
       <c r="G301" s="6" t="s">
@@ -16208,19 +16208,19 @@
     </row>
     <row r="302" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A302" s="10" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B302" s="13">
         <v>20220826</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="D302" s="1">
         <v>299</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="F302" s="6"/>
       <c r="G302" s="6" t="s">
@@ -16239,19 +16239,19 @@
     </row>
     <row r="303" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A303" s="10" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B303" s="13">
         <v>20220826</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="D303" s="1">
         <v>300</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="F303" s="6"/>
       <c r="G303" s="6" t="s">
@@ -16270,19 +16270,19 @@
     </row>
     <row r="304" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A304" s="10" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="B304" s="13">
         <v>20220826</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="D304" s="1">
         <v>301</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="F304" s="6"/>
       <c r="G304" s="6" t="s">
@@ -16301,19 +16301,19 @@
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A305" s="10" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B305" s="13">
         <v>20220826</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="D305" s="1">
         <v>302</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="F305" s="6"/>
       <c r="G305" s="6" t="s">
@@ -16332,23 +16332,23 @@
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A306" s="10" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B306" s="13">
         <v>20220826</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="D306" s="1">
         <v>303</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="F306" s="6"/>
       <c r="G306" s="6" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="H306" s="6" t="s">
         <v>13</v>
@@ -16363,23 +16363,23 @@
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A307" s="10" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B307" s="13">
         <v>20220826</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="D307" s="1">
         <v>304</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="F307" s="6"/>
       <c r="G307" s="6" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="H307" s="6" t="s">
         <v>13</v>
@@ -16394,19 +16394,19 @@
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A308" s="10" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="B308" s="13">
         <v>20220826</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="D308" s="1">
         <v>305</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F308" s="6"/>
       <c r="G308" s="6" t="s">
@@ -16425,19 +16425,19 @@
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A309" s="10" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="B309" s="13">
         <v>20220826</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="D309" s="1">
         <v>306</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="F309" s="6"/>
       <c r="G309" s="6" t="s">
@@ -16456,19 +16456,19 @@
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A310" s="10" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B310" s="13">
         <v>20220826</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="D310" s="1">
         <v>307</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="F310" s="6"/>
       <c r="G310" s="6" t="s">
@@ -16487,19 +16487,19 @@
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A311" s="10" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B311" s="13">
         <v>20220826</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="D311" s="1">
         <v>308</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="F311" s="6"/>
       <c r="G311" s="6" t="s">
@@ -16518,19 +16518,19 @@
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A312" s="10" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B312" s="13">
         <v>20220826</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D312" s="1">
         <v>309</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="F312" s="6"/>
       <c r="G312" s="6" t="s">
@@ -16549,19 +16549,19 @@
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A313" s="10" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B313" s="13">
         <v>20220826</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="D313" s="1">
         <v>310</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="F313" s="6"/>
       <c r="G313" s="6" t="s">
@@ -16580,19 +16580,19 @@
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A314" s="10" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="B314" s="13">
         <v>20220826</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="D314" s="1">
         <v>311</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="F314" s="6"/>
       <c r="G314" s="6" t="s">
@@ -16611,19 +16611,19 @@
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A315" s="10" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="B315" s="13">
         <v>20220826</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="D315" s="1">
         <v>312</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="F315" s="6"/>
       <c r="G315" s="6" t="s">
@@ -16642,19 +16642,19 @@
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A316" s="10" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="B316" s="13">
         <v>20220826</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="D316" s="1">
         <v>313</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="F316" s="6"/>
       <c r="G316" s="6" t="s">
@@ -16673,19 +16673,19 @@
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A317" s="10" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="B317" s="13">
         <v>20220826</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="D317" s="1">
         <v>314</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="F317" s="6"/>
       <c r="G317" s="6" t="s">
@@ -16698,25 +16698,25 @@
         <v>161</v>
       </c>
       <c r="J317" s="6" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="K317" s="2"/>
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A318" s="10" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="B318" s="13">
         <v>20220826</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D318" s="1">
         <v>315</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="F318" s="6"/>
       <c r="G318" s="6" t="s">
@@ -16735,19 +16735,19 @@
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A319" s="10" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B319" s="13">
         <v>20220826</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="D319" s="1">
         <v>316</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="F319" s="6"/>
       <c r="G319" s="6" t="s">
@@ -16757,7 +16757,7 @@
         <v>13</v>
       </c>
       <c r="I319" s="6" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="J319" s="6" t="s">
         <v>94</v>
@@ -16766,19 +16766,19 @@
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A320" s="10" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="B320" s="13">
         <v>20220826</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="D320" s="1">
         <v>317</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="F320" s="6"/>
       <c r="G320" s="6" t="s">
@@ -16797,19 +16797,19 @@
     </row>
     <row r="321" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A321" s="10" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="B321" s="13">
         <v>20220826</v>
       </c>
       <c r="C321" s="15" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="D321" s="3">
         <v>318</v>
       </c>
       <c r="E321" s="4" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="F321" s="15"/>
       <c r="G321" s="15" t="s">
@@ -16819,13 +16819,13 @@
         <v>13</v>
       </c>
       <c r="I321" s="15" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="J321" s="15" t="s">
         <v>145</v>
       </c>
       <c r="K321" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="L321" s="15" t="s">
         <v>79</v>
@@ -16834,7 +16834,7 @@
         <v>13</v>
       </c>
       <c r="N321" s="15" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="O321" s="15" t="s">
         <v>145</v>
@@ -16842,19 +16842,19 @@
     </row>
     <row r="322" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A322" s="10" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="B322" s="13">
         <v>20220826</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="D322" s="1">
         <v>319</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="F322" s="6"/>
       <c r="G322" s="6" t="s">
@@ -16873,19 +16873,19 @@
     </row>
     <row r="323" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A323" s="10" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="B323" s="13">
         <v>20220826</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="D323" s="1">
         <v>320</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="F323" s="6"/>
       <c r="G323" s="6" t="s">
@@ -16904,19 +16904,19 @@
     </row>
     <row r="324" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A324" s="10" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="B324" s="13">
         <v>20220826</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="D324" s="1">
         <v>321</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="F324" s="6"/>
       <c r="G324" s="6" t="s">
@@ -16935,19 +16935,19 @@
     </row>
     <row r="325" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A325" s="10" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="B325" s="13">
         <v>20220826</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="D325" s="1">
         <v>322</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="F325" s="6"/>
       <c r="G325" s="6" t="s">
@@ -16966,19 +16966,19 @@
     </row>
     <row r="326" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A326" s="10" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="B326" s="13">
         <v>20220826</v>
       </c>
       <c r="C326" s="6" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="D326" s="1">
         <v>323</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="F326" s="6"/>
       <c r="G326" s="6" t="s">
@@ -16997,19 +16997,19 @@
     </row>
     <row r="327" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A327" s="10" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="B327" s="13">
         <v>20220826</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="D327" s="1">
         <v>324</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="F327" s="6"/>
       <c r="G327" s="6" t="s">
@@ -17028,19 +17028,19 @@
     </row>
     <row r="328" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A328" s="10" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="B328" s="13">
         <v>20220826</v>
       </c>
       <c r="C328" s="6" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="D328" s="1">
         <v>325</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="F328" s="6"/>
       <c r="G328" s="6" t="s">
@@ -17059,19 +17059,19 @@
     </row>
     <row r="329" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A329" s="10" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="B329" s="13">
         <v>20220826</v>
       </c>
       <c r="C329" s="6" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="D329" s="1">
         <v>326</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="F329" s="6"/>
       <c r="G329" s="6" t="s">
@@ -17090,19 +17090,19 @@
     </row>
     <row r="330" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A330" s="10" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="B330" s="13">
         <v>20220826</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D330" s="1">
         <v>327</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="F330" s="6"/>
       <c r="G330" s="6" t="s">
@@ -17121,19 +17121,19 @@
     </row>
     <row r="331" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A331" s="10" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="B331" s="13">
         <v>20220826</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="D331" s="1">
         <v>328</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="F331" s="6"/>
       <c r="G331" s="6" t="s">
@@ -17152,19 +17152,19 @@
     </row>
     <row r="332" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A332" s="10" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="B332" s="13">
         <v>20220826</v>
       </c>
       <c r="C332" s="6" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="D332" s="1">
         <v>329</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="F332" s="6"/>
       <c r="G332" s="6" t="s">
@@ -17174,7 +17174,7 @@
         <v>13</v>
       </c>
       <c r="I332" s="6" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="J332" s="6" t="s">
         <v>114</v>
@@ -17183,19 +17183,19 @@
     </row>
     <row r="333" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A333" s="10" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="B333" s="13">
         <v>20220826</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="D333" s="1">
         <v>330</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="F333" s="6"/>
       <c r="G333" s="6" t="s">
@@ -17214,19 +17214,19 @@
     </row>
     <row r="334" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A334" s="10" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="B334" s="13">
         <v>20220826</v>
       </c>
       <c r="C334" s="15" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="D334" s="3">
         <v>331</v>
       </c>
       <c r="E334" s="4" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="F334" s="15"/>
       <c r="G334" s="15" t="s">
@@ -17242,7 +17242,7 @@
         <v>72</v>
       </c>
       <c r="K334" s="4" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="L334" s="15" t="s">
         <v>151</v>
@@ -17259,19 +17259,19 @@
     </row>
     <row r="335" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A335" s="10" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="B335" s="13">
         <v>20220826</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="D335" s="1">
         <v>332</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="F335" s="6"/>
       <c r="G335" s="6" t="s">
@@ -17290,19 +17290,19 @@
     </row>
     <row r="336" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A336" s="10" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="B336" s="13">
         <v>20220826</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="D336" s="1">
         <v>333</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="F336" s="6"/>
       <c r="G336" s="6" t="s">
@@ -17312,7 +17312,7 @@
         <v>13</v>
       </c>
       <c r="I336" s="6" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="J336" s="6" t="s">
         <v>50</v>
@@ -17321,19 +17321,19 @@
     </row>
     <row r="337" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A337" s="10" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="B337" s="13">
         <v>20220826</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="D337" s="1">
         <v>334</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="F337" s="6"/>
       <c r="G337" s="6" t="s">
@@ -17352,19 +17352,19 @@
     </row>
     <row r="338" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A338" s="10" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="B338" s="13">
         <v>20220826</v>
       </c>
       <c r="C338" s="6" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="D338" s="1">
         <v>335</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="F338" s="6"/>
       <c r="G338" s="6" t="s">
@@ -17383,19 +17383,19 @@
     </row>
     <row r="339" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A339" s="10" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="B339" s="13">
         <v>20220826</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="D339" s="1">
         <v>336</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="F339" s="6"/>
       <c r="G339" s="6" t="s">
@@ -17414,19 +17414,19 @@
     </row>
     <row r="340" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A340" s="10" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="B340" s="13">
         <v>20220826</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="D340" s="1">
         <v>337</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="F340" s="6"/>
       <c r="G340" s="6" t="s">
@@ -17445,19 +17445,19 @@
     </row>
     <row r="341" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A341" s="10" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="B341" s="13">
         <v>20220826</v>
       </c>
       <c r="C341" s="6" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D341" s="1">
         <v>338</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="F341" s="6"/>
       <c r="G341" s="6" t="s">
@@ -17476,19 +17476,19 @@
     </row>
     <row r="342" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A342" s="10" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="B342" s="13">
         <v>20220826</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="D342" s="1">
         <v>339</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="F342" s="6"/>
       <c r="G342" s="6" t="s">
@@ -17507,19 +17507,19 @@
     </row>
     <row r="343" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A343" s="10" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="B343" s="13">
         <v>20220826</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="D343" s="1">
         <v>340</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="F343" s="6"/>
       <c r="G343" s="6" t="s">
@@ -17538,19 +17538,19 @@
     </row>
     <row r="344" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A344" s="10" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="B344" s="13">
         <v>20220826</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="D344" s="1">
         <v>341</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="F344" s="6"/>
       <c r="G344" s="6" t="s">
@@ -17569,19 +17569,19 @@
     </row>
     <row r="345" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A345" s="10" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="B345" s="13">
         <v>20220826</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="D345" s="1">
         <v>342</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="F345" s="6"/>
       <c r="G345" s="6" t="s">
@@ -17600,19 +17600,19 @@
     </row>
     <row r="346" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A346" s="10" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="B346" s="13">
         <v>20220826</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D346" s="1">
         <v>343</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="F346" s="6"/>
       <c r="G346" s="6" t="s">
@@ -17631,19 +17631,19 @@
     </row>
     <row r="347" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A347" s="10" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="B347" s="13">
         <v>20220826</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D347" s="1">
         <v>344</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="F347" s="6"/>
       <c r="G347" s="6" t="s">
@@ -17662,19 +17662,19 @@
     </row>
     <row r="348" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A348" s="10" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="B348" s="13">
         <v>20220826</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="D348" s="1">
         <v>345</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="F348" s="6"/>
       <c r="G348" s="6" t="s">
@@ -17693,19 +17693,19 @@
     </row>
     <row r="349" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A349" s="10" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="B349" s="13">
         <v>20220826</v>
       </c>
       <c r="C349" s="6" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="D349" s="1">
         <v>346</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="F349" s="6"/>
       <c r="G349" s="6" t="s">
@@ -17724,19 +17724,19 @@
     </row>
     <row r="350" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A350" s="10" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="B350" s="13">
         <v>20220826</v>
       </c>
       <c r="C350" s="6" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="D350" s="1">
         <v>347</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="F350" s="6"/>
       <c r="G350" s="6" t="s">
@@ -17755,19 +17755,19 @@
     </row>
     <row r="351" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A351" s="10" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="B351" s="13">
         <v>20220826</v>
       </c>
       <c r="C351" s="15" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="D351" s="3">
         <v>348</v>
       </c>
       <c r="E351" s="4" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="F351" s="15"/>
       <c r="G351" s="15" t="s">
@@ -17783,7 +17783,7 @@
         <v>29</v>
       </c>
       <c r="K351" s="4" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="L351" s="15" t="s">
         <v>11</v>
@@ -17800,19 +17800,19 @@
     </row>
     <row r="352" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A352" s="10" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="B352" s="13">
         <v>20220826</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="D352" s="1">
         <v>349</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="F352" s="6"/>
       <c r="G352" s="6" t="s">
@@ -17822,7 +17822,7 @@
         <v>13</v>
       </c>
       <c r="I352" s="6" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="J352" s="6" t="s">
         <v>55</v>
@@ -17831,19 +17831,19 @@
     </row>
     <row r="353" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A353" s="10" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="B353" s="13">
         <v>20220826</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="D353" s="1">
         <v>350</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="F353" s="6"/>
       <c r="G353" s="6" t="s">
@@ -17862,19 +17862,19 @@
     </row>
     <row r="354" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A354" s="10" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="B354" s="13">
         <v>20220826</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="D354" s="1">
         <v>351</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="F354" s="6"/>
       <c r="G354" s="6" t="s">
@@ -17891,24 +17891,24 @@
       </c>
       <c r="K354" s="2"/>
       <c r="P354" s="7" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="355" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A355" s="10" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="B355" s="13">
         <v>20220826</v>
       </c>
       <c r="C355" s="6" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="D355" s="1">
         <v>352</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="F355" s="6"/>
       <c r="G355" s="6" t="s">
@@ -17927,19 +17927,19 @@
     </row>
     <row r="356" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A356" s="10" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="B356" s="13">
         <v>20220826</v>
       </c>
       <c r="C356" s="6" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="D356" s="1">
         <v>353</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="F356" s="6"/>
       <c r="G356" s="6" t="s">
@@ -17958,19 +17958,19 @@
     </row>
     <row r="357" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A357" s="10" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="B357" s="13">
         <v>20220826</v>
       </c>
       <c r="C357" s="6" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="D357" s="1">
         <v>354</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="F357" s="6"/>
       <c r="G357" s="6" t="s">
@@ -17989,19 +17989,19 @@
     </row>
     <row r="358" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A358" s="10" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="B358" s="13">
         <v>20220826</v>
       </c>
       <c r="C358" s="6" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="D358" s="1">
         <v>355</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="F358" s="6"/>
       <c r="G358" s="6" t="s">
@@ -18020,23 +18020,23 @@
     </row>
     <row r="359" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A359" s="10" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="B359" s="13">
         <v>20220826</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="D359" s="1">
         <v>356</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="F359" s="6"/>
       <c r="G359" s="6" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="H359" s="6" t="s">
         <v>13</v>
@@ -18051,19 +18051,19 @@
     </row>
     <row r="360" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A360" s="10" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="B360" s="13">
         <v>20220826</v>
       </c>
       <c r="C360" s="6" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="D360" s="1">
         <v>357</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="F360" s="6"/>
       <c r="G360" s="6" t="s">
@@ -18073,7 +18073,7 @@
         <v>13</v>
       </c>
       <c r="I360" s="6" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="J360" s="6" t="s">
         <v>106</v>
@@ -18082,19 +18082,19 @@
     </row>
     <row r="361" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A361" s="10" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="B361" s="13">
         <v>20220826</v>
       </c>
       <c r="C361" s="15" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="D361" s="3">
         <v>358</v>
       </c>
       <c r="E361" s="4" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="F361" s="15"/>
       <c r="G361" s="15" t="s">
@@ -18110,7 +18110,7 @@
         <v>72</v>
       </c>
       <c r="K361" s="4" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="L361" s="15" t="s">
         <v>339</v>
@@ -18127,19 +18127,19 @@
     </row>
     <row r="362" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A362" s="10" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="B362" s="13">
         <v>20220826</v>
       </c>
       <c r="C362" s="6" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="D362" s="1">
         <v>359</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="F362" s="6"/>
       <c r="G362" s="6" t="s">
@@ -18158,19 +18158,19 @@
     </row>
     <row r="363" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A363" s="10" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="B363" s="13">
         <v>20220826</v>
       </c>
       <c r="C363" s="6" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="D363" s="1">
         <v>360</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="F363" s="6"/>
       <c r="G363" s="6" t="s">
@@ -18189,19 +18189,19 @@
     </row>
     <row r="364" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A364" s="10" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B364" s="13">
         <v>20220826</v>
       </c>
       <c r="C364" s="6" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="D364" s="1">
         <v>361</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="F364" s="6"/>
       <c r="G364" s="6" t="s">
@@ -18220,19 +18220,19 @@
     </row>
     <row r="365" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A365" s="10" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="B365" s="13">
         <v>20220826</v>
       </c>
       <c r="C365" s="6" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="D365" s="1">
         <v>362</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="F365" s="6"/>
       <c r="G365" s="6" t="s">
@@ -18242,7 +18242,7 @@
         <v>13</v>
       </c>
       <c r="I365" s="6" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="J365" s="6" t="s">
         <v>68</v>
@@ -18251,19 +18251,19 @@
     </row>
     <row r="366" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A366" s="10" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B366" s="13">
         <v>20220826</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="D366" s="1">
         <v>363</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="F366" s="6"/>
       <c r="G366" s="6" t="s">
@@ -18282,19 +18282,19 @@
     </row>
     <row r="367" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A367" s="10" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="B367" s="13">
         <v>20220826</v>
       </c>
       <c r="C367" s="6" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="D367" s="1">
         <v>364</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="F367" s="6"/>
       <c r="G367" s="6" t="s">
@@ -18313,19 +18313,19 @@
     </row>
     <row r="368" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A368" s="10" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B368" s="13">
         <v>20220826</v>
       </c>
       <c r="C368" s="6" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="D368" s="1">
         <v>365</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="F368" s="6"/>
       <c r="G368" s="6" t="s">
@@ -18344,19 +18344,19 @@
     </row>
     <row r="369" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A369" s="10" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="B369" s="13">
         <v>20220826</v>
       </c>
       <c r="C369" s="6" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="D369" s="1">
         <v>366</v>
       </c>
       <c r="E369" s="2" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="F369" s="6"/>
       <c r="G369" s="6" t="s">
@@ -18375,19 +18375,19 @@
     </row>
     <row r="370" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A370" s="10" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="B370" s="13">
         <v>20220826</v>
       </c>
       <c r="C370" s="6" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="D370" s="1">
         <v>367</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="F370" s="6"/>
       <c r="G370" s="6" t="s">
@@ -18406,19 +18406,19 @@
     </row>
     <row r="371" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A371" s="10" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B371" s="13">
         <v>20220826</v>
       </c>
       <c r="C371" s="6" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="D371" s="1">
         <v>368</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="F371" s="6"/>
       <c r="G371" s="6" t="s">
@@ -18437,19 +18437,19 @@
     </row>
     <row r="372" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A372" s="10" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="B372" s="13">
         <v>20220826</v>
       </c>
       <c r="C372" s="6" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="D372" s="1">
         <v>369</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="F372" s="6"/>
       <c r="G372" s="6" t="s">
@@ -18468,19 +18468,19 @@
     </row>
     <row r="373" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A373" s="10" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="B373" s="13">
         <v>20220826</v>
       </c>
       <c r="C373" s="6" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="D373" s="1">
         <v>370</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="F373" s="6"/>
       <c r="G373" s="6" t="s">
@@ -18499,19 +18499,19 @@
     </row>
     <row r="374" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A374" s="10" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="B374" s="13">
         <v>20220826</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="D374" s="1">
         <v>371</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="F374" s="6"/>
       <c r="G374" s="6" t="s">
@@ -18530,19 +18530,19 @@
     </row>
     <row r="375" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A375" s="10" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="B375" s="13">
         <v>20220826</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="D375" s="1">
         <v>372</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="F375" s="6"/>
       <c r="G375" s="6" t="s">
@@ -18561,19 +18561,19 @@
     </row>
     <row r="376" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A376" s="10" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="B376" s="13">
         <v>20220826</v>
       </c>
       <c r="C376" s="6" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="D376" s="1">
         <v>373</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="F376" s="6"/>
       <c r="G376" s="6" t="s">
@@ -18592,19 +18592,19 @@
     </row>
     <row r="377" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A377" s="10" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="B377" s="13">
         <v>20220826</v>
       </c>
       <c r="C377" s="6" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="D377" s="1">
         <v>374</v>
       </c>
       <c r="E377" s="2" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="F377" s="6"/>
       <c r="G377" s="6" t="s">
@@ -18623,19 +18623,19 @@
     </row>
     <row r="378" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A378" s="10" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="B378" s="13">
         <v>20220826</v>
       </c>
       <c r="C378" s="6" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="D378" s="1">
         <v>375</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="F378" s="6"/>
       <c r="G378" s="6" t="s">
@@ -18654,19 +18654,19 @@
     </row>
     <row r="379" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A379" s="10" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="B379" s="13">
         <v>20220826</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="D379" s="1">
         <v>376</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="F379" s="6"/>
       <c r="G379" s="6" t="s">
@@ -18689,19 +18689,19 @@
     </row>
     <row r="380" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A380" s="10" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="B380" s="13">
         <v>20220826</v>
       </c>
       <c r="C380" s="15" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="D380" s="3">
         <v>377</v>
       </c>
       <c r="E380" s="4" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="F380" s="15"/>
       <c r="G380" s="15" t="s">
@@ -18717,7 +18717,7 @@
         <v>271</v>
       </c>
       <c r="K380" s="4" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="L380" s="15" t="s">
         <v>178</v>
@@ -18734,19 +18734,19 @@
     </row>
     <row r="381" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A381" s="10" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="B381" s="13">
         <v>20220826</v>
       </c>
       <c r="C381" s="6" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="D381" s="1">
         <v>378</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="F381" s="6"/>
       <c r="G381" s="6" t="s">
@@ -18759,25 +18759,25 @@
         <v>71</v>
       </c>
       <c r="J381" s="6" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="K381" s="2"/>
     </row>
     <row r="382" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A382" s="10" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="B382" s="13">
         <v>20220826</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="D382" s="1">
         <v>379</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="F382" s="6"/>
       <c r="G382" s="6" t="s">
@@ -18796,19 +18796,19 @@
     </row>
     <row r="383" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A383" s="10" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="B383" s="13">
         <v>20220826</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="D383" s="1">
         <v>380</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="F383" s="6"/>
       <c r="G383" s="6" t="s">
@@ -18827,19 +18827,19 @@
     </row>
     <row r="384" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A384" s="10" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="B384" s="13">
         <v>20220826</v>
       </c>
       <c r="C384" s="6" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="D384" s="1">
         <v>381</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="F384" s="6"/>
       <c r="G384" s="6" t="s">
@@ -18849,7 +18849,7 @@
         <v>13</v>
       </c>
       <c r="I384" s="6" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="J384" s="6" t="s">
         <v>68</v>
@@ -18858,19 +18858,19 @@
     </row>
     <row r="385" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A385" s="10" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B385" s="13">
         <v>20220826</v>
       </c>
       <c r="C385" s="6" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D385" s="1">
         <v>382</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="F385" s="6"/>
       <c r="G385" s="6" t="s">
@@ -18889,19 +18889,19 @@
     </row>
     <row r="386" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A386" s="10" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="B386" s="13">
         <v>20220826</v>
       </c>
       <c r="C386" s="6" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="D386" s="1">
         <v>383</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="F386" s="6"/>
       <c r="G386" s="6" t="s">
@@ -18920,19 +18920,19 @@
     </row>
     <row r="387" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A387" s="10" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="B387" s="13">
         <v>20220826</v>
       </c>
       <c r="C387" s="15" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="D387" s="3">
         <v>384</v>
       </c>
       <c r="E387" s="4" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="F387" s="15"/>
       <c r="G387" s="15" t="s">
@@ -18948,7 +18948,7 @@
         <v>145</v>
       </c>
       <c r="K387" s="4" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="L387" s="15" t="s">
         <v>427</v>
@@ -18965,19 +18965,19 @@
     </row>
     <row r="388" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A388" s="10" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="B388" s="13">
         <v>20220826</v>
       </c>
       <c r="C388" s="6" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="D388" s="1">
         <v>385</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="F388" s="6"/>
       <c r="G388" s="6" t="s">
@@ -18996,19 +18996,19 @@
     </row>
     <row r="389" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A389" s="10" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="B389" s="13">
         <v>20220826</v>
       </c>
       <c r="C389" s="6" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="D389" s="1">
         <v>386</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="F389" s="6"/>
       <c r="G389" s="6" t="s">
@@ -19018,7 +19018,7 @@
         <v>13</v>
       </c>
       <c r="I389" s="6" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="J389" s="6" t="s">
         <v>50</v>
@@ -19027,19 +19027,19 @@
     </row>
     <row r="390" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A390" s="10" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="B390" s="13">
         <v>20220826</v>
       </c>
       <c r="C390" s="6" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="D390" s="1">
         <v>387</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="F390" s="6"/>
       <c r="G390" s="6" t="s">
@@ -19049,7 +19049,7 @@
         <v>13</v>
       </c>
       <c r="I390" s="6" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="J390" s="6" t="s">
         <v>110</v>
@@ -19058,19 +19058,19 @@
     </row>
     <row r="391" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A391" s="10" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="B391" s="13">
         <v>20220826</v>
       </c>
       <c r="C391" s="6" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="D391" s="1">
         <v>388</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="F391" s="6"/>
       <c r="G391" s="6" t="s">
@@ -19080,28 +19080,28 @@
         <v>13</v>
       </c>
       <c r="I391" s="6" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="J391" s="6" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="K391" s="2"/>
     </row>
     <row r="392" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A392" s="10" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="B392" s="13">
         <v>20220826</v>
       </c>
       <c r="C392" s="6" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="D392" s="1">
         <v>389</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="F392" s="6"/>
       <c r="G392" s="6" t="s">
@@ -19120,19 +19120,19 @@
     </row>
     <row r="393" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A393" s="10" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="B393" s="13">
         <v>20220826</v>
       </c>
       <c r="C393" s="6" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="D393" s="1">
         <v>390</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="F393" s="6"/>
       <c r="G393" s="6" t="s">
@@ -19151,23 +19151,23 @@
     </row>
     <row r="394" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A394" s="10" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="B394" s="13">
         <v>20220826</v>
       </c>
       <c r="C394" s="6" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="D394" s="1">
         <v>391</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="F394" s="6"/>
       <c r="G394" s="6" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="H394" s="6" t="s">
         <v>13</v>
@@ -19182,19 +19182,19 @@
     </row>
     <row r="395" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A395" s="10" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="B395" s="13">
         <v>20220826</v>
       </c>
       <c r="C395" s="6" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="D395" s="1">
         <v>392</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F395" s="6"/>
       <c r="G395" s="6" t="s">
@@ -19213,19 +19213,19 @@
     </row>
     <row r="396" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A396" s="10" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="B396" s="13">
         <v>20220826</v>
       </c>
       <c r="C396" s="6" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="D396" s="1">
         <v>393</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="F396" s="6"/>
       <c r="G396" s="6" t="s">
@@ -19244,19 +19244,19 @@
     </row>
     <row r="397" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A397" s="10" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="B397" s="13">
         <v>20220826</v>
       </c>
       <c r="C397" s="6" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="D397" s="1">
         <v>394</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="F397" s="6"/>
       <c r="G397" s="6" t="s">
@@ -19266,7 +19266,7 @@
         <v>13</v>
       </c>
       <c r="I397" s="6" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="J397" s="6" t="s">
         <v>29</v>
@@ -19275,19 +19275,19 @@
     </row>
     <row r="398" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A398" s="10" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="B398" s="13">
         <v>20220826</v>
       </c>
       <c r="C398" s="6" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="D398" s="1">
         <v>395</v>
       </c>
       <c r="E398" s="2" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="F398" s="6"/>
       <c r="G398" s="6" t="s">
@@ -19306,19 +19306,19 @@
     </row>
     <row r="399" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A399" s="10" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="B399" s="13">
         <v>20220826</v>
       </c>
       <c r="C399" s="6" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="D399" s="1">
         <v>396</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="F399" s="6"/>
       <c r="G399" s="6" t="s">
@@ -19328,7 +19328,7 @@
         <v>13</v>
       </c>
       <c r="I399" s="6" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="J399" s="6" t="s">
         <v>29</v>
@@ -19337,19 +19337,19 @@
     </row>
     <row r="400" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A400" s="10" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="B400" s="13">
         <v>20220826</v>
       </c>
       <c r="C400" s="6" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="D400" s="1">
         <v>397</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="F400" s="6"/>
       <c r="G400" s="6" t="s">
@@ -19372,19 +19372,19 @@
     </row>
     <row r="401" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A401" s="10" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="B401" s="13">
         <v>20220826</v>
       </c>
       <c r="C401" s="15" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="D401" s="3">
         <v>398</v>
       </c>
       <c r="E401" s="4" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F401" s="15"/>
       <c r="G401" s="15" t="s">
@@ -19400,7 +19400,7 @@
         <v>110</v>
       </c>
       <c r="K401" s="4" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="L401" s="15" t="s">
         <v>113</v>
@@ -19417,19 +19417,19 @@
     </row>
     <row r="402" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A402" s="10" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="B402" s="13">
         <v>20220826</v>
       </c>
       <c r="C402" s="6" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="D402" s="8">
         <v>399</v>
       </c>
       <c r="E402" s="9" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="F402" s="6"/>
       <c r="G402" s="6" t="s">
@@ -19453,19 +19453,19 @@
     </row>
     <row r="403" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A403" s="10" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="B403" s="13">
         <v>20220826</v>
       </c>
       <c r="C403" s="6" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="D403" s="1">
         <v>400</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="F403" s="6"/>
       <c r="G403" s="6" t="s">
@@ -19484,19 +19484,19 @@
     </row>
     <row r="404" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A404" s="10" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="B404" s="13">
         <v>20220826</v>
       </c>
       <c r="C404" s="6" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="D404" s="1">
         <v>401</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="F404" s="6"/>
       <c r="G404" s="6" t="s">
@@ -19515,19 +19515,19 @@
     </row>
     <row r="405" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A405" s="10" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="B405" s="13">
         <v>20220826</v>
       </c>
       <c r="C405" s="6" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="D405" s="1">
         <v>402</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="F405" s="6"/>
       <c r="G405" s="6" t="s">
@@ -19546,19 +19546,19 @@
     </row>
     <row r="406" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A406" s="10" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="B406" s="13">
         <v>20220826</v>
       </c>
       <c r="C406" s="6" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="D406" s="1">
         <v>403</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="F406" s="6"/>
       <c r="G406" s="6" t="s">
@@ -19577,19 +19577,19 @@
     </row>
     <row r="407" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A407" s="10" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="B407" s="13">
         <v>20220826</v>
       </c>
       <c r="C407" s="6" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="D407" s="1">
         <v>404</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="F407" s="6"/>
       <c r="G407" s="6" t="s">
@@ -19608,19 +19608,19 @@
     </row>
     <row r="408" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A408" s="10" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="B408" s="13">
         <v>20220826</v>
       </c>
       <c r="C408" s="6" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="D408" s="1">
         <v>405</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="F408" s="6"/>
       <c r="G408" s="6" t="s">
@@ -19639,19 +19639,19 @@
     </row>
     <row r="409" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A409" s="10" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="B409" s="13">
         <v>20220826</v>
       </c>
       <c r="C409" s="15" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="D409" s="3">
         <v>406</v>
       </c>
       <c r="E409" s="4" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="F409" s="15"/>
       <c r="G409" s="15" t="s">
@@ -19667,7 +19667,7 @@
         <v>55</v>
       </c>
       <c r="K409" s="4" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="L409" s="15" t="s">
         <v>178</v>
@@ -19684,19 +19684,19 @@
     </row>
     <row r="410" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A410" s="10" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="B410" s="13">
         <v>20220826</v>
       </c>
       <c r="C410" s="6" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="D410" s="1">
         <v>407</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F410" s="6"/>
       <c r="G410" s="6" t="s">
@@ -19713,24 +19713,24 @@
       </c>
       <c r="K410" s="2"/>
       <c r="P410" s="7" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="411" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A411" s="10" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="B411" s="13">
         <v>20220826</v>
       </c>
       <c r="C411" s="6" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="D411" s="1">
         <v>408</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="F411" s="6"/>
       <c r="G411" s="6" t="s">
@@ -19749,19 +19749,19 @@
     </row>
     <row r="412" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A412" s="10" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="B412" s="13">
         <v>20220826</v>
       </c>
       <c r="C412" s="6" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="D412" s="1">
         <v>409</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="F412" s="6"/>
       <c r="G412" s="6" t="s">
@@ -19780,19 +19780,19 @@
     </row>
     <row r="413" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A413" s="10" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="B413" s="13">
         <v>20220826</v>
       </c>
       <c r="C413" s="6" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="D413" s="1">
         <v>410</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="F413" s="6"/>
       <c r="G413" s="6" t="s">
@@ -19811,19 +19811,19 @@
     </row>
     <row r="414" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A414" s="10" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="B414" s="13">
         <v>20220826</v>
       </c>
       <c r="C414" s="6" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="D414" s="1">
         <v>411</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="F414" s="6"/>
       <c r="G414" s="6" t="s">
@@ -19840,24 +19840,24 @@
       </c>
       <c r="K414" s="2"/>
       <c r="P414" s="7" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="415" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A415" s="10" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="B415" s="13">
         <v>20220826</v>
       </c>
       <c r="C415" s="6" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="D415" s="1">
         <v>412</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="F415" s="6"/>
       <c r="G415" s="6" t="s">
@@ -19876,19 +19876,19 @@
     </row>
     <row r="416" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A416" s="10" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="B416" s="13">
         <v>20220826</v>
       </c>
       <c r="C416" s="6" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="D416" s="1">
         <v>413</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="F416" s="6"/>
       <c r="G416" s="6" t="s">
@@ -19907,19 +19907,19 @@
     </row>
     <row r="417" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A417" s="10" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="B417" s="13">
         <v>20220826</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="D417" s="1">
         <v>414</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="F417" s="6"/>
       <c r="G417" s="6" t="s">
@@ -19938,19 +19938,19 @@
     </row>
     <row r="418" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A418" s="10" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="B418" s="13">
         <v>20220826</v>
       </c>
       <c r="C418" s="15" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="D418" s="3">
         <v>415</v>
       </c>
       <c r="E418" s="4" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="F418" s="15"/>
       <c r="G418" s="15" t="s">
@@ -19966,7 +19966,7 @@
         <v>106</v>
       </c>
       <c r="K418" s="4" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="L418" s="15" t="s">
         <v>109</v>
@@ -19983,19 +19983,19 @@
     </row>
     <row r="419" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A419" s="10" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="B419" s="13">
         <v>20220826</v>
       </c>
       <c r="C419" s="6" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="D419" s="1">
         <v>416</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="F419" s="6"/>
       <c r="G419" s="6" t="s">
@@ -20014,19 +20014,19 @@
     </row>
     <row r="420" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A420" s="10" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="B420" s="13">
         <v>20220826</v>
       </c>
       <c r="C420" s="6" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="D420" s="1">
         <v>417</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F420" s="6"/>
       <c r="G420" s="6" t="s">
@@ -20045,19 +20045,19 @@
     </row>
     <row r="421" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A421" s="10" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="B421" s="13">
         <v>20220826</v>
       </c>
       <c r="C421" s="6" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="D421" s="1">
         <v>418</v>
       </c>
       <c r="E421" s="2" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F421" s="6"/>
       <c r="G421" s="6" t="s">
@@ -20076,19 +20076,19 @@
     </row>
     <row r="422" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A422" s="10" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="B422" s="13">
         <v>20220826</v>
       </c>
       <c r="C422" s="6" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="D422" s="1">
         <v>419</v>
       </c>
       <c r="E422" s="2" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="F422" s="6"/>
       <c r="G422" s="6" t="s">
@@ -20111,19 +20111,19 @@
     </row>
     <row r="423" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A423" s="10" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="B423" s="13">
         <v>20220826</v>
       </c>
       <c r="C423" s="15" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="D423" s="3">
         <v>420</v>
       </c>
       <c r="E423" s="4" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="F423" s="15"/>
       <c r="G423" s="15" t="s">
@@ -20139,7 +20139,7 @@
         <v>33</v>
       </c>
       <c r="K423" s="4" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="L423" s="15" t="s">
         <v>188</v>
@@ -20156,19 +20156,19 @@
     </row>
     <row r="424" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A424" s="10" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="B424" s="13">
         <v>20220826</v>
       </c>
       <c r="C424" s="6" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="D424" s="8">
         <v>421</v>
       </c>
       <c r="E424" s="9" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="F424" s="6"/>
       <c r="G424" s="6" t="s">
@@ -20187,19 +20187,19 @@
     </row>
     <row r="425" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A425" s="10" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="B425" s="13">
         <v>20220826</v>
       </c>
       <c r="C425" s="6" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="D425" s="1">
         <v>422</v>
       </c>
       <c r="E425" s="2" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="F425" s="6"/>
       <c r="G425" s="6" t="s">
@@ -20218,19 +20218,19 @@
     </row>
     <row r="426" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A426" s="10" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="B426" s="13">
         <v>20220826</v>
       </c>
       <c r="C426" s="6" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="D426" s="1">
         <v>423</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="F426" s="6"/>
       <c r="G426" s="6" t="s">
@@ -20249,19 +20249,19 @@
     </row>
     <row r="427" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A427" s="10" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="B427" s="13">
         <v>20220826</v>
       </c>
       <c r="C427" s="6" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="D427" s="1">
         <v>424</v>
       </c>
       <c r="E427" s="2" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="F427" s="6"/>
       <c r="G427" s="6" t="s">
@@ -20280,19 +20280,19 @@
     </row>
     <row r="428" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A428" s="10" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="B428" s="13">
         <v>20220826</v>
       </c>
       <c r="C428" s="6" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="D428" s="1">
         <v>425</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="F428" s="6"/>
       <c r="G428" s="6" t="s">
@@ -20311,19 +20311,19 @@
     </row>
     <row r="429" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A429" s="10" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="B429" s="13">
         <v>20220826</v>
       </c>
       <c r="C429" s="6" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="D429" s="1">
         <v>426</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="F429" s="6"/>
       <c r="G429" s="6" t="s">
@@ -20342,19 +20342,19 @@
     </row>
     <row r="430" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A430" s="10" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="B430" s="13">
         <v>20220826</v>
       </c>
       <c r="C430" s="6" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="D430" s="1">
         <v>427</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="F430" s="6"/>
       <c r="G430" s="6" t="s">
@@ -20373,19 +20373,19 @@
     </row>
     <row r="431" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A431" s="10" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="B431" s="13">
         <v>20220826</v>
       </c>
       <c r="C431" s="6" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="D431" s="1">
         <v>428</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="F431" s="6"/>
       <c r="G431" s="6" t="s">
@@ -20404,19 +20404,19 @@
     </row>
     <row r="432" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A432" s="10" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="B432" s="13">
         <v>20220826</v>
       </c>
       <c r="C432" s="6" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="D432" s="1">
         <v>429</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="F432" s="6"/>
       <c r="G432" s="6" t="s">
@@ -20435,19 +20435,19 @@
     </row>
     <row r="433" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A433" s="10" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="B433" s="13">
         <v>20220826</v>
       </c>
       <c r="C433" s="6" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="D433" s="1">
         <v>430</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="F433" s="6"/>
       <c r="G433" s="6" t="s">
@@ -20470,19 +20470,19 @@
     </row>
     <row r="434" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A434" s="10" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="B434" s="13">
         <v>20220826</v>
       </c>
       <c r="C434" s="15" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="D434" s="3">
         <v>431</v>
       </c>
       <c r="E434" s="4" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="F434" s="15"/>
       <c r="G434" s="15" t="s">
@@ -20498,7 +20498,7 @@
         <v>68</v>
       </c>
       <c r="K434" s="4" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="L434" s="15" t="s">
         <v>27</v>
@@ -20515,19 +20515,19 @@
     </row>
     <row r="435" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A435" s="10" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="B435" s="13">
         <v>20220826</v>
       </c>
       <c r="C435" s="6" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="D435" s="1">
         <v>432</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="F435" s="6"/>
       <c r="G435" s="6" t="s">
@@ -20546,23 +20546,23 @@
     </row>
     <row r="436" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A436" s="10" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="B436" s="13">
         <v>20220826</v>
       </c>
       <c r="C436" s="6" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="D436" s="1">
         <v>433</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="F436" s="6"/>
       <c r="G436" s="6" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="H436" s="6" t="s">
         <v>13</v>
@@ -20577,23 +20577,23 @@
     </row>
     <row r="437" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A437" s="10" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="B437" s="13">
         <v>20220826</v>
       </c>
       <c r="C437" s="6" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="D437" s="1">
         <v>434</v>
       </c>
       <c r="E437" s="2" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="F437" s="6"/>
       <c r="G437" s="6" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="H437" s="6" t="s">
         <v>13</v>
@@ -20608,23 +20608,23 @@
     </row>
     <row r="438" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A438" s="10" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="B438" s="13">
         <v>20220826</v>
       </c>
       <c r="C438" s="6" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="D438" s="1">
         <v>435</v>
       </c>
       <c r="E438" s="2" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="F438" s="6"/>
       <c r="G438" s="6" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="H438" s="6" t="s">
         <v>13</v>
@@ -20633,29 +20633,29 @@
         <v>592</v>
       </c>
       <c r="J438" s="6" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="K438" s="2"/>
     </row>
     <row r="439" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A439" s="10" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="B439" s="13">
         <v>20220826</v>
       </c>
       <c r="C439" s="6" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="D439" s="1">
         <v>436</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="F439" s="6"/>
       <c r="G439" s="6" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="H439" s="6" t="s">
         <v>13</v>
@@ -20670,19 +20670,19 @@
     </row>
     <row r="440" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A440" s="10" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="B440" s="13">
         <v>20220826</v>
       </c>
       <c r="C440" s="6" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="D440" s="1">
         <v>437</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="F440" s="6"/>
       <c r="G440" s="6" t="s">
@@ -20701,23 +20701,23 @@
     </row>
     <row r="441" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A441" s="10" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="B441" s="13">
         <v>20220826</v>
       </c>
       <c r="C441" s="6" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="D441" s="1">
         <v>438</v>
       </c>
       <c r="E441" s="2" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="F441" s="6"/>
       <c r="G441" s="6" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="H441" s="6" t="s">
         <v>13</v>
@@ -20732,19 +20732,19 @@
     </row>
     <row r="442" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A442" s="10" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="B442" s="13">
         <v>20220826</v>
       </c>
       <c r="C442" s="15" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="D442" s="3">
         <v>439</v>
       </c>
       <c r="E442" s="4" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="F442" s="15"/>
       <c r="G442" s="15" t="s">
@@ -20760,7 +20760,7 @@
         <v>72</v>
       </c>
       <c r="K442" s="4" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="L442" s="15" t="s">
         <v>137</v>
@@ -20777,19 +20777,19 @@
     </row>
     <row r="443" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A443" s="10" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B443" s="13">
         <v>20220826</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="D443" s="1">
         <v>440</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="F443" s="6"/>
       <c r="G443" s="6" t="s">
@@ -21039,10 +21039,10 @@
         <v>769</v>
       </c>
       <c r="D450" s="3" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="E450" s="4" t="s">
-        <v>888</v>
+        <v>1636</v>
       </c>
       <c r="F450" s="15" t="s">
         <v>13</v>
@@ -21079,7 +21079,7 @@
         <v>98</v>
       </c>
       <c r="E451" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F451" s="15" t="s">
         <v>13</v>
@@ -21116,7 +21116,7 @@
         <v>109</v>
       </c>
       <c r="E452" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F452" s="15" t="s">
         <v>13</v>
@@ -21150,10 +21150,10 @@
         <v>775</v>
       </c>
       <c r="D453" s="3" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E453" s="4" t="s">
         <v>1637</v>
-      </c>
-      <c r="E453" s="4" t="s">
-        <v>932</v>
       </c>
       <c r="F453" s="15" t="s">
         <v>13</v>
@@ -21190,7 +21190,7 @@
         <v>135</v>
       </c>
       <c r="E454" s="4" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="F454" s="15" t="s">
         <v>13</v>
@@ -21227,7 +21227,7 @@
         <v>149</v>
       </c>
       <c r="E455" s="4" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="F455" s="15" t="s">
         <v>13</v>
@@ -21264,7 +21264,7 @@
         <v>159</v>
       </c>
       <c r="E456" s="4" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="F456" s="15" t="s">
         <v>13</v>
@@ -21301,7 +21301,7 @@
         <v>172</v>
       </c>
       <c r="E457" s="4" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="F457" s="15" t="s">
         <v>13</v>
@@ -21338,7 +21338,7 @@
         <v>185</v>
       </c>
       <c r="E458" s="4" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="F458" s="15" t="s">
         <v>13</v>
@@ -21375,7 +21375,7 @@
         <v>202</v>
       </c>
       <c r="E459" s="4" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="F459" s="15" t="s">
         <v>13</v>
@@ -21412,7 +21412,7 @@
         <v>211</v>
       </c>
       <c r="E460" s="4" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="F460" s="15" t="s">
         <v>13</v>
@@ -21449,7 +21449,7 @@
         <v>228</v>
       </c>
       <c r="E461" s="4" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="F461" s="15" t="s">
         <v>13</v>
@@ -21486,7 +21486,7 @@
         <v>233</v>
       </c>
       <c r="E462" s="4" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="F462" s="15" t="s">
         <v>13</v>
@@ -21523,7 +21523,7 @@
         <v>250</v>
       </c>
       <c r="E463" s="4" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="F463" s="15" t="s">
         <v>13</v>
@@ -21560,7 +21560,7 @@
         <v>259</v>
       </c>
       <c r="E464" s="4" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F464" s="15" t="s">
         <v>13</v>
@@ -21597,7 +21597,7 @@
         <v>280</v>
       </c>
       <c r="E465" s="4" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="F465" s="15" t="s">
         <v>13</v>
@@ -21634,7 +21634,7 @@
         <v>290</v>
       </c>
       <c r="E466" s="4" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="F466" s="15" t="s">
         <v>13</v>
@@ -21659,19 +21659,19 @@
     </row>
     <row r="467" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A467" s="10" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="B467" s="13">
         <v>20220826</v>
       </c>
       <c r="C467" s="15" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="D467" s="3">
         <v>297</v>
       </c>
       <c r="E467" s="4" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="F467" s="16"/>
       <c r="G467" s="15" t="s">
@@ -21694,19 +21694,19 @@
     </row>
     <row r="468" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A468" s="10" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="B468" s="13">
         <v>20220826</v>
       </c>
       <c r="C468" s="15" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="D468" s="3">
         <v>318</v>
       </c>
       <c r="E468" s="4" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="F468" s="16"/>
       <c r="G468" s="15" t="s">
@@ -21716,7 +21716,7 @@
         <v>13</v>
       </c>
       <c r="I468" s="15" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="J468" s="15" t="s">
         <v>145</v>
@@ -21729,19 +21729,19 @@
     </row>
     <row r="469" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A469" s="10" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="B469" s="13">
         <v>20220826</v>
       </c>
       <c r="C469" s="15" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="D469" s="3">
         <v>331</v>
       </c>
       <c r="E469" s="4" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="F469" s="16"/>
       <c r="G469" s="15" t="s">
@@ -21764,19 +21764,19 @@
     </row>
     <row r="470" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A470" s="10" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="B470" s="13">
         <v>20220826</v>
       </c>
       <c r="C470" s="15" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="D470" s="3">
         <v>348</v>
       </c>
       <c r="E470" s="4" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="F470" s="16"/>
       <c r="G470" s="15" t="s">
@@ -21799,19 +21799,19 @@
     </row>
     <row r="471" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A471" s="10" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="B471" s="13">
         <v>20220826</v>
       </c>
       <c r="C471" s="15" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="D471" s="3">
         <v>377</v>
       </c>
       <c r="E471" s="4" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="F471" s="16"/>
       <c r="G471" s="15" t="s">
@@ -21834,19 +21834,19 @@
     </row>
     <row r="472" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A472" s="10" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="B472" s="13">
         <v>20220826</v>
       </c>
       <c r="C472" s="15" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="D472" s="3">
         <v>384</v>
       </c>
       <c r="E472" s="4" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="F472" s="16"/>
       <c r="G472" s="15" t="s">
@@ -21869,19 +21869,19 @@
     </row>
     <row r="473" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A473" s="10" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="B473" s="13">
         <v>20220826</v>
       </c>
       <c r="C473" s="15" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="D473" s="3">
         <v>398</v>
       </c>
       <c r="E473" s="4" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F473" s="16"/>
       <c r="G473" s="15" t="s">
@@ -21904,19 +21904,19 @@
     </row>
     <row r="474" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A474" s="10" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="B474" s="13">
         <v>20220826</v>
       </c>
       <c r="C474" s="15" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="D474" s="3">
         <v>406</v>
       </c>
       <c r="E474" s="4" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="F474" s="16"/>
       <c r="G474" s="15" t="s">
@@ -21939,19 +21939,19 @@
     </row>
     <row r="475" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A475" s="10" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="B475" s="13">
         <v>20220826</v>
       </c>
       <c r="C475" s="15" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="D475" s="3">
         <v>415</v>
       </c>
       <c r="E475" s="4" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="F475" s="16"/>
       <c r="G475" s="15" t="s">
@@ -21974,19 +21974,19 @@
     </row>
     <row r="476" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A476" s="10" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="B476" s="13">
         <v>20220826</v>
       </c>
       <c r="C476" s="15" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="D476" s="3">
         <v>420</v>
       </c>
       <c r="E476" s="4" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="F476" s="16"/>
       <c r="G476" s="15" t="s">
@@ -22009,19 +22009,19 @@
     </row>
     <row r="477" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A477" s="10" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="B477" s="13">
         <v>20220826</v>
       </c>
       <c r="C477" s="15" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="D477" s="3">
         <v>431</v>
       </c>
       <c r="E477" s="4" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="F477" s="16"/>
       <c r="G477" s="15" t="s">
@@ -22044,19 +22044,19 @@
     </row>
     <row r="478" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A478" s="10" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="B478" s="13">
         <v>20220826</v>
       </c>
       <c r="C478" s="15" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="D478" s="3">
         <v>439</v>
       </c>
       <c r="E478" s="4" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="F478" s="16"/>
       <c r="G478" s="15" t="s">
@@ -22079,19 +22079,19 @@
     </row>
     <row r="479" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A479" s="10" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="B479" s="13">
         <v>20220826</v>
       </c>
       <c r="C479" s="15" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="D479" s="3">
         <v>358</v>
       </c>
       <c r="E479" s="4" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="F479" s="16"/>
       <c r="G479" s="15" t="s">
